--- a/cleaning_forms/014_metal_cleaning_checklist--cleaning_forms.xlsx
+++ b/cleaning_forms/014_metal_cleaning_checklist--cleaning_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -877,12 +877,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>notes_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Notes 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -900,12 +900,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>metal_surface_condition</t>
+          <t>metal_surface_condition_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Metal Surface Condition</t>
+          <t>Metal Surface Condition 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -923,12 +923,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>metal_surface_area</t>
+          <t>metal_surface_area_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Metal Surface Area</t>
+          <t>Metal Surface Area 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>metal_condition_before_service</t>
+          <t>metal_condition_before_service_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Metal Condition Before Service</t>
+          <t>Metal Condition Before Service 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>metal_condition_after_service</t>
+          <t>metal_condition_after_service_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Metal Condition After Service</t>
+          <t>Metal Condition After Service 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1084,12 +1084,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>metal_cleaning_checklist</t>
+          <t>metal_cleaning_checklist_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Metal Cleaning Checklist</t>
+          <t>Metal Cleaning Checklist 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1110,12 +1110,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1160,29 +1160,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>metal_area_without_paint_choices</t>
+          <t>metal_area_with_paint_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1211,29 +1211,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>metal_area_with_coating_choices</t>
+          <t>metal_area_without_paint_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1245,114 +1245,199 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>metal_area_without_coating_choices</t>
+          <t>metal_area_with_coating_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>metal_area_without_coating_choices</t>
+          <t>metal_area_with_coating_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>metal_area_with_clearing_choices</t>
+          <t>metal_area_without_coating_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>metal_area_with_clearing_choices</t>
+          <t>metal_area_without_coating_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>metal_area_without_clearing_choices</t>
+          <t>metal_area_without_coating_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>metal_area_with_clearing_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>metal_area_with_clearing_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>metal_area_with_clearing_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>metal_area_without_clearing_choices</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>option2</t>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>metal_area_without_clearing_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>metal_area_without_clearing_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Other</t>
         </is>
       </c>
     </row>
